--- a/table_des_routes-exemple-2.xlsx
+++ b/table_des_routes-exemple-2.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shoni/Documents/DevProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\begin\OneDrive\Documents\VINCI_bloc1\HTML\Projet_TypeScript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD4453BD-49CD-C74E-9A40-A53746BE98DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC4819F-54D2-4B71-90AA-0D7ED4336E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17060" xr2:uid="{6911F376-5DDD-4D7B-A61B-D86E41227354}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="1" xr2:uid="{6911F376-5DDD-4D7B-A61B-D86E41227354}"/>
   </bookViews>
   <sheets>
     <sheet name="Module 1   Users" sheetId="2" r:id="rId1"/>
     <sheet name="Module 2    Games" sheetId="3" r:id="rId2"/>
-    <sheet name="Module 3 Teams" sheetId="4" r:id="rId3"/>
-    <sheet name="Module 4 Fields" sheetId="5" r:id="rId4"/>
+    <sheet name="Module 4 Fields" sheetId="5" r:id="rId3"/>
+    <sheet name="Module 3 Teams" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="156">
   <si>
     <t>Table des routes</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Paramètres de query</t>
   </si>
   <si>
-    <t>XX</t>
-  </si>
-  <si>
     <t>Groupe :</t>
   </si>
   <si>
@@ -108,9 +105,6 @@
   </si>
   <si>
     <t>/users</t>
-  </si>
-  <si>
-    <t>400 : username déjà existant ou role non valide</t>
   </si>
   <si>
     <t>PATCH</t>
@@ -146,19 +140,7 @@
     <t>Admin et arbitres</t>
   </si>
   <si>
-    <t>400 : utilisateur inexistant ou invalid username</t>
-  </si>
-  <si>
-    <t>récupère un utilisateur sur base de son username</t>
-  </si>
-  <si>
     <t>email : l'email de l'utilisateur</t>
-  </si>
-  <si>
-    <t>400 : utilisateur inexistant ou invalid email</t>
-  </si>
-  <si>
-    <t>récupère un utilisateur sur base de son email</t>
   </si>
   <si>
     <r>
@@ -208,62 +190,13 @@
     <t>id : identifiant de l'utilisateur</t>
   </si>
   <si>
-    <t>200 : Utilisateur créé :UserDTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200 : Liste des users : UserDTO[] </t>
-  </si>
-  <si>
     <t>200 : L'utilisateur recherché : UserDTO</t>
-  </si>
-  <si>
-    <t>200 : Infos basic du user : BasicUserDTO{id, firstName,Username}</t>
-  </si>
-  <si>
-    <t>401 : non authentifié || 404 : utilisateur introuvable</t>
   </si>
   <si>
     <t>récupère les infos basiques d'un user sur base de son ID</t>
   </si>
   <si>
-    <t>PATCH /users/id/role/:role</t>
-  </si>
-  <si>
-    <t>/users/id/role/:role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200 : Mise à jour du player </t>
-  </si>
-  <si>
-    <t>400 : player invalide
-404 : player introuvable</t>
-  </si>
-  <si>
-    <t>Mise à jour des infos d'un player par l'administrateur</t>
-  </si>
-  <si>
-    <t>PATCH/users/id/status/:status</t>
-  </si>
-  <si>
     <t xml:space="preserve">users </t>
-  </si>
-  <si>
-    <t>/users/id/status/:status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status: le status du user </t>
-  </si>
-  <si>
-    <t>role : le role d'un user</t>
-  </si>
-  <si>
-    <t>200 : Modification du status du user : UserDTO</t>
-  </si>
-  <si>
-    <t>400 : user invalide   || 404 : user introuvable</t>
-  </si>
-  <si>
-    <t>Changement du status par l'admin ou par la demande de l'user à l'admin</t>
   </si>
   <si>
     <t>games</t>
@@ -275,25 +208,13 @@
     <t>/games/status/:status</t>
   </si>
   <si>
-    <t>status: le status du game</t>
-  </si>
-  <si>
     <t>Changement du status d'un match</t>
-  </si>
-  <si>
-    <t>Arbitres, Admin, Entraineur</t>
-  </si>
-  <si>
-    <t>PATCH /games/status/:status</t>
   </si>
   <si>
     <t>POST /games</t>
   </si>
   <si>
     <t>/games</t>
-  </si>
-  <si>
-    <t>PUT /games</t>
   </si>
   <si>
     <t>05</t>
@@ -308,13 +229,7 @@
     <t>PUT/users/:id</t>
   </si>
   <si>
-    <t>role : EROLES</t>
-  </si>
-  <si>
     <t>200 : User mis à jour : UserDTO</t>
-  </si>
-  <si>
-    <t>400 : role invalide ou user != player  | 403 : accès interdit | 404: User introuvable</t>
   </si>
   <si>
     <t xml:space="preserve">Récupère la liste des games </t>
@@ -356,19 +271,7 @@
     <t>Met à jour les infos d'un game scheduled.</t>
   </si>
   <si>
-    <t>{status: "cancelled"|"started"|"finished"}</t>
-  </si>
-  <si>
     <t>200 : Mise à jour du status du match : GameDTO</t>
-  </si>
-  <si>
-    <t>PATCH /games/score/:score</t>
-  </si>
-  <si>
-    <t>/games/score/:score</t>
-  </si>
-  <si>
-    <t>score : le score du match</t>
   </si>
   <si>
     <t>{homeScore: number,
@@ -385,9 +288,6 @@
   </si>
   <si>
     <t>GET /games/:id</t>
-  </si>
-  <si>
-    <t>DELETE/games</t>
   </si>
   <si>
     <t>DELETE</t>
@@ -407,18 +307,6 @@
   </si>
   <si>
     <t>400 : données invalides( terrain déjà réservé ce jour, game cancelled/finished)
-401 : pas authentifié
-403 : accès refusé
-404 : jeu introuvable</t>
-  </si>
-  <si>
-    <t>400 : score invalide, game n'a pas encore "started"
-401 : pas authentifié
-403 : accès refusé (Forbidden vu au cours)
-404 : game introuvable</t>
-  </si>
-  <si>
-    <t>400 : changement de statut invalide
 401 : pas authentifié
 403 : accès refusé
 404 : jeu introuvable</t>
@@ -539,12 +427,172 @@
   <si>
     <t>Création d'un nouveau terrain avec un nom unique.</t>
   </si>
+  <si>
+    <t>PATCH /users/:id/role/:role</t>
+  </si>
+  <si>
+    <t>User authentifier</t>
+  </si>
+  <si>
+    <t>Utilisateur changé: UserToUpdateDTO</t>
+  </si>
+  <si>
+    <t>200 : Liste des users : BasicUserDTO[]</t>
+  </si>
+  <si>
+    <t>récupère un utilisateur sur base de son username et renvoie un UserDTO sans l'attribut "password".</t>
+  </si>
+  <si>
+    <t>récupère un utilisateur sur base de son email et renvoie un UserDTO sans l'attribut "password".</t>
+  </si>
+  <si>
+    <t>DELETE/users/:id</t>
+  </si>
+  <si>
+    <t>Admin et le User lui-même</t>
+  </si>
+  <si>
+    <t>Le User lui-même</t>
+  </si>
+  <si>
+    <t>201 : Utilisateur créé :UserDTO</t>
+  </si>
+  <si>
+    <t>200: User mis à "inactif".</t>
+  </si>
+  <si>
+    <t>Inactive un User autre qu'un Admin en le mettant à "inactif".</t>
+  </si>
+  <si>
+    <t>400 : liste de User vide ou role non valide</t>
+  </si>
+  <si>
+    <t>(Si Admin) 200: L'utilisateur recherché: UserDTO                                                    (Si Autre User) 200: L'utilisateur recherché: BasicUserDTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400: id doit être un nombre                                                                      404: User inéxistant avec ce id                                                          403 : accès interdit                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">400: id doit être un nombre                                                                      404: User inéxistant avec ce id                                                              400: User est un Admin, impossible de l'inactiver                                                          403 : accès interdit  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">400 : User invalide                                                                                 403 : accès interdit                                                                              404: User introuvable                                                                           400: id doit être un nombre </t>
+  </si>
+  <si>
+    <t>400 : username déjà existant                                                            400: email déjà éxistant                                                                      400:  User Invalide</t>
+  </si>
+  <si>
+    <t>400 : utilisateur inexistant                                                                      400 :email invalide                                                                                400: accès interdit</t>
+  </si>
+  <si>
+    <t>400 : utilisateur inexistant                                                                400:invalid username                                                                               400: accès interdit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changement du role d'un User "player" par l'admin. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH/users/id/status/:status  </t>
+  </si>
+  <si>
+    <t>200 : Modification du role du User "player" : UserDTO</t>
+  </si>
+  <si>
+    <t>400 : User invalide                                                                                 403 : accès interdit                                                                              404: User introuvable                                                                           400: id doit être un nombre                                                                400: role invalide                                                                               400: user n'est pas un "player"</t>
+  </si>
+  <si>
+    <t>/users/:id/role/:role</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /users/:id/status/:status</t>
+  </si>
+  <si>
+    <t>id: l'id du User "player"                                                                                            role : le nouveau role</t>
+  </si>
+  <si>
+    <t>id: l'id du User                                                                                             status: le nouveau status</t>
+  </si>
+  <si>
+    <t>200 : Mise à jour du status du User</t>
+  </si>
+  <si>
+    <t>400: id doit être un nombre                                                                      404: User inéxistant avec ce id                                                              400: User est un Admin, impossible de l'inactiver                                                          403 : accès interdit</t>
+  </si>
+  <si>
+    <t>PATCH /games/:id/status/:status</t>
+  </si>
+  <si>
+    <t>id: l'id du game                                                  status: le nouveau status</t>
+  </si>
+  <si>
+    <t>Arbitres, Admin , Entraineur</t>
+  </si>
+  <si>
+    <t>400 : game status invalide
+401 : pas authentifié
+403 : accès refusé (Forbidden vu au cours)
+404 : game introuvable</t>
+  </si>
+  <si>
+    <t>PATCH /games/score/:id</t>
+  </si>
+  <si>
+    <t>/games/score/:id</t>
+  </si>
+  <si>
+    <t>id: l'id du game</t>
+  </si>
+  <si>
+    <t>PUT /games/:id</t>
+  </si>
+  <si>
+    <t>DELETE/games/:id</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">400 : changement de statut invalide
+401 : pas authentifié </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>??</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Qui n'est pas auth.(==accés refusè)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+403 : accès refusé
+404 : jeu introuvable</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,6 +638,22 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -742,13 +806,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -797,13 +872,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Titre 1" xfId="1" builtinId="16"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="28">
     <dxf>
       <font>
         <strike val="0"/>
@@ -833,18 +907,40 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -859,6 +955,58 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -879,7 +1027,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1207770</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -1009,7 +1157,7 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1672590</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -1120,6 +1268,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="fr-BE" sz="1100" i="0" kern="1200">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1139,7 +1288,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>811530</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -1269,7 +1418,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>895350</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -1399,7 +1548,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>857250</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -1529,7 +1678,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1169670</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -1659,7 +1808,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1131570</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -1789,7 +1938,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1177290</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -1919,7 +2068,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1687830</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2049,7 +2198,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>2122170</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2179,7 +2328,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>807720</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2309,7 +2458,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>891540</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2439,7 +2588,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>861060</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2569,7 +2718,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1173480</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2699,7 +2848,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1127760</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2829,7 +2978,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1165860</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2959,7 +3108,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1211580</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -3089,7 +3238,7 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1661160</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -3200,6 +3349,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="fr-BE" sz="1100" i="0" kern="1200">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -3219,7 +3369,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1691640</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -3349,7 +3499,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>2110740</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -3479,7 +3629,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>811530</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -3610,7 +3760,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1169670</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -3741,7 +3891,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1131570</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -3872,7 +4022,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1177290</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -4003,7 +4153,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>2122170</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -4139,7 +4289,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1207770</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -4270,7 +4420,7 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1672590</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -4401,7 +4551,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>811530</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -4532,7 +4682,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>895350</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -4663,7 +4813,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>857250</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -4794,7 +4944,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1169670</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -4925,7 +5075,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1131570</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -5056,7 +5206,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1177290</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -5187,7 +5337,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1687830</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -5318,7 +5468,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>2122170</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -5449,7 +5599,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>807720</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -5580,7 +5730,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>891540</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -5711,7 +5861,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>861060</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -5842,7 +5992,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1173480</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -5973,7 +6123,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1127760</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -6104,7 +6254,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1165860</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -6235,7 +6385,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1211580</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -6366,7 +6516,7 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1661160</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -6497,7 +6647,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1691640</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -6628,7 +6778,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>2110740</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -6759,7 +6909,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>811530</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -6890,7 +7040,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1169670</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -7021,7 +7171,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1131570</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -7152,7 +7302,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1177290</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -7283,7 +7433,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>2122170</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -7423,22 +7573,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="ZoneTexte 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A74B3F85-C9E8-4540-B0E9-1982A489C160}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15596870" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A2FBD50-8251-8544-BE36-9069795AD11F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15596870" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7488,21 +7638,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="ZoneTexte 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A74B3F85-C9E8-4540-B0E9-1982A489C160}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15596870" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A2FBD50-8251-8544-BE36-9069795AD11F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15596870" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7554,22 +7704,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="ZoneTexte 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2177D463-F20E-8242-AF01-CE3F2F9D3340}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="21827490" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CC599E2-288F-6848-BA15-F917E554F56D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21827490" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7619,21 +7769,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="ZoneTexte 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2177D463-F20E-8242-AF01-CE3F2F9D3340}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="21827490" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CC599E2-288F-6848-BA15-F917E554F56D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21827490" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7685,22 +7835,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="ZoneTexte 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1F293A0-C02B-9248-926B-4ABC5DC996B7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="811530" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B7BA945-EFA5-3C45-8BA8-6B9548685BEB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="811530" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7750,21 +7900,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="ZoneTexte 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1F293A0-C02B-9248-926B-4ABC5DC996B7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="811530" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B7BA945-EFA5-3C45-8BA8-6B9548685BEB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="811530" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7816,22 +7966,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="ZoneTexte 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92BA2357-355F-A847-B99E-D48788DB728B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3854450" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4434DFEE-8D09-D449-A204-BD55A924562A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3854450" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7881,21 +8031,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="ZoneTexte 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92BA2357-355F-A847-B99E-D48788DB728B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3854450" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4434DFEE-8D09-D449-A204-BD55A924562A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3854450" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7947,22 +8097,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="ZoneTexte 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BECB4D1-EBF5-4543-9F9A-2DDB882044B8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5721350" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74ED3430-1FF5-D046-B0BA-A1298989DB6F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5721350" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8012,21 +8162,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="ZoneTexte 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BECB4D1-EBF5-4543-9F9A-2DDB882044B8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5721350" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74ED3430-1FF5-D046-B0BA-A1298989DB6F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5721350" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8078,22 +8228,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="ZoneTexte 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB611A0-1155-A64A-B558-D59BBE4FF54E}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7938770" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{286B98E5-BF37-8C48-84F7-DB22D5C428DB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7938770" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8143,21 +8293,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="ZoneTexte 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB611A0-1155-A64A-B558-D59BBE4FF54E}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7938770" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{286B98E5-BF37-8C48-84F7-DB22D5C428DB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7938770" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8209,22 +8359,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="ZoneTexte 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0554AFC0-D439-7A40-89D5-8E3813742834}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10440670" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1E844B-63D8-7A4B-BFBD-183E464E3847}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10440670" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8274,21 +8424,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="ZoneTexte 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0554AFC0-D439-7A40-89D5-8E3813742834}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10440670" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1E844B-63D8-7A4B-BFBD-183E464E3847}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10440670" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8340,22 +8490,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="ZoneTexte 8">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C48D286B-C6E6-B747-A5EE-87EFA649753B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13026390" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E1A1524-56F4-5342-94DD-460BF5F4CE45}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13026390" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8405,21 +8555,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="ZoneTexte 8">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C48D286B-C6E6-B747-A5EE-87EFA649753B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13026390" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E1A1524-56F4-5342-94DD-460BF5F4CE45}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13026390" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8471,22 +8621,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="ZoneTexte 9">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92913276-7F21-C840-99D2-54750B521DF7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25652730" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16984F06-64BA-2D4B-8514-332ED08369FC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25652730" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8536,21 +8686,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="ZoneTexte 9">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92913276-7F21-C840-99D2-54750B521DF7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25652730" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16984F06-64BA-2D4B-8514-332ED08369FC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25652730" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8602,22 +8752,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="ZoneTexte 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E96AF6B-F546-1543-AF04-B90DBB4F0CE5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29897070" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE6FEF86-3F15-2641-B432-4D38513B6E3B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29897070" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8667,21 +8817,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="ZoneTexte 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E96AF6B-F546-1543-AF04-B90DBB4F0CE5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29897070" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE6FEF86-3F15-2641-B432-4D38513B6E3B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29897070" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8733,22 +8883,22 @@
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="ZoneTexte 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA0C0F04-39DA-1C49-87DE-80C4FC9A4EEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="807720" y="6535420"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2ED5ACA-D27B-B144-AA3B-D043DCE53A84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="807720" y="5709920"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8798,21 +8948,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="ZoneTexte 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA0C0F04-39DA-1C49-87DE-80C4FC9A4EEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="807720" y="6535420"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2ED5ACA-D27B-B144-AA3B-D043DCE53A84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="807720" y="5709920"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8864,22 +9014,22 @@
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="ZoneTexte 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89704287-484E-3543-B6DC-DE7F22F21F5D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3850640" y="6558280"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59A3DB9B-4C5F-D24E-BE9D-2CA43D9C8692}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3850640" y="5732780"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8929,21 +9079,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="ZoneTexte 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89704287-484E-3543-B6DC-DE7F22F21F5D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3850640" y="6558280"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59A3DB9B-4C5F-D24E-BE9D-2CA43D9C8692}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3850640" y="5732780"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -8995,22 +9145,22 @@
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="ZoneTexte 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7139E79-75C6-E648-ABD7-3C132FAFE7B8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5725160" y="6543040"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34E3559D-E614-6F44-959F-387FD3A32DD1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5725160" y="5717540"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9060,21 +9210,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="ZoneTexte 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7139E79-75C6-E648-ABD7-3C132FAFE7B8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5725160" y="6543040"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34E3559D-E614-6F44-959F-387FD3A32DD1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5725160" y="5717540"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9126,22 +9276,22 @@
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="ZoneTexte 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99EB8D60-4CEA-D242-9A7C-732654B247EC}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7942580" y="6535420"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C7C186-151F-A44E-A3D6-6617C9016025}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7942580" y="5709920"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9191,21 +9341,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="ZoneTexte 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99EB8D60-4CEA-D242-9A7C-732654B247EC}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7942580" y="6535420"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C7C186-151F-A44E-A3D6-6617C9016025}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7942580" y="5709920"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9257,22 +9407,22 @@
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="ZoneTexte 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{584D3F77-7BF3-634E-A4F7-902A859D7D89}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10436860" y="6543040"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38366437-7667-AF47-84F7-BD2C37E5B4E0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10436860" y="5717540"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9322,21 +9472,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="ZoneTexte 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{584D3F77-7BF3-634E-A4F7-902A859D7D89}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10436860" y="6543040"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38366437-7667-AF47-84F7-BD2C37E5B4E0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10436860" y="5717540"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9388,22 +9538,22 @@
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="ZoneTexte 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E04118B-6A44-A443-BF44-6866EE33AA44}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13014960" y="6535420"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1446D2D4-E27C-0749-B7F0-51D90646D470}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13014960" y="5709920"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9453,21 +9603,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="ZoneTexte 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E04118B-6A44-A443-BF44-6866EE33AA44}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13014960" y="6535420"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1446D2D4-E27C-0749-B7F0-51D90646D470}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13014960" y="5709920"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9519,22 +9669,22 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="ZoneTexte 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2F1E364-E47E-6247-B340-C566248F9E62}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15600680" y="6550660"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70407851-3306-C445-94A0-C9DBA0DBEF5A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15600680" y="5725160"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9584,21 +9734,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="ZoneTexte 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2F1E364-E47E-6247-B340-C566248F9E62}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15600680" y="6550660"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70407851-3306-C445-94A0-C9DBA0DBEF5A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15600680" y="5725160"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9650,22 +9800,22 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="ZoneTexte 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF5E56F-7981-4843-BFD2-AEF7EA1A7645}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="21816060" y="6550660"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E42C189D-B0C9-E247-8888-A9B152AD13D9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21816060" y="5725160"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9715,21 +9865,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="ZoneTexte 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF5E56F-7981-4843-BFD2-AEF7EA1A7645}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="21816060" y="6550660"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E42C189D-B0C9-E247-8888-A9B152AD13D9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21816060" y="5725160"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9781,22 +9931,22 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="20" name="ZoneTexte 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91B778C3-FEF6-1A43-8954-648876841033}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25656540" y="6550660"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5002B184-6C45-E743-A8F4-D613A67B9494}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25656540" y="5725160"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9846,21 +9996,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="20" name="ZoneTexte 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91B778C3-FEF6-1A43-8954-648876841033}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25656540" y="6550660"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5002B184-6C45-E743-A8F4-D613A67B9494}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25656540" y="5725160"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9912,22 +10062,22 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="ZoneTexte 20">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1D530DC-EDFA-EA43-8EA7-5787DEE042EB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29885640" y="6550660"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A4939D2-AD03-F04F-9C8F-84A036AF3F81}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29885640" y="5725160"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -9977,21 +10127,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="ZoneTexte 20">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1D530DC-EDFA-EA43-8EA7-5787DEE042EB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29885640" y="6550660"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A4939D2-AD03-F04F-9C8F-84A036AF3F81}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29885640" y="5725160"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10043,22 +10193,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="ZoneTexte 21">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{901C8334-E527-2D49-A247-C07C67E4A125}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="811530" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9D825B-533D-C44A-B645-28229152AB3F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="811530" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10108,21 +10258,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="ZoneTexte 21">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{901C8334-E527-2D49-A247-C07C67E4A125}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="811530" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9D825B-533D-C44A-B645-28229152AB3F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="811530" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10174,22 +10324,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="ZoneTexte 22">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7CCA624-6449-D247-B2D9-E505724B8685}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7938770" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32CCE455-0CC5-A848-A58C-02998F3E4A9D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7938770" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10239,21 +10389,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="ZoneTexte 22">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7CCA624-6449-D247-B2D9-E505724B8685}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7938770" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32CCE455-0CC5-A848-A58C-02998F3E4A9D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7938770" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10305,22 +10455,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="ZoneTexte 23">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F6BCC8-2215-E649-B5B7-78A679C6760C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10440670" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC29AA4F-57ED-684A-80AC-096B07559CB4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10440670" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10370,21 +10520,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="ZoneTexte 23">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F6BCC8-2215-E649-B5B7-78A679C6760C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10440670" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC29AA4F-57ED-684A-80AC-096B07559CB4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10440670" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10436,22 +10586,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="ZoneTexte 24">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FA9E705-540C-4F42-A208-1E36A062FF00}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13026390" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFAC8F2-E1A0-6649-93D9-03055B1E87AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13026390" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10501,21 +10651,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="ZoneTexte 24">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FA9E705-540C-4F42-A208-1E36A062FF00}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13026390" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFAC8F2-E1A0-6649-93D9-03055B1E87AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13026390" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10567,22 +10717,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="ZoneTexte 25">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{842A4576-CA79-F54C-BA87-F94B251D5A06}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29897070" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A02D5546-BF61-3248-8FF7-2E87F6D3DE0B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29897070" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10632,21 +10782,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="ZoneTexte 25">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{842A4576-CA79-F54C-BA87-F94B251D5A06}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29897070" y="6527800"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A02D5546-BF61-3248-8FF7-2E87F6D3DE0B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29897070" y="5702300"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10703,22 +10853,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="ZoneTexte 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A2FBD50-8251-8544-BE36-9069795AD11F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15596870" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A74B3F85-C9E8-4540-B0E9-1982A489C160}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15596870" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10768,21 +10918,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="ZoneTexte 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A2FBD50-8251-8544-BE36-9069795AD11F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15596870" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A74B3F85-C9E8-4540-B0E9-1982A489C160}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15596870" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10834,22 +10984,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="ZoneTexte 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CC599E2-288F-6848-BA15-F917E554F56D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="21827490" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2177D463-F20E-8242-AF01-CE3F2F9D3340}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21827490" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10899,21 +11049,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="ZoneTexte 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CC599E2-288F-6848-BA15-F917E554F56D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="21827490" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2177D463-F20E-8242-AF01-CE3F2F9D3340}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21827490" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10965,22 +11115,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="ZoneTexte 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B7BA945-EFA5-3C45-8BA8-6B9548685BEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="811530" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1F293A0-C02B-9248-926B-4ABC5DC996B7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="811530" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11030,21 +11180,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="ZoneTexte 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B7BA945-EFA5-3C45-8BA8-6B9548685BEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="811530" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1F293A0-C02B-9248-926B-4ABC5DC996B7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="811530" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11096,22 +11246,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="ZoneTexte 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4434DFEE-8D09-D449-A204-BD55A924562A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3854450" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92BA2357-355F-A847-B99E-D48788DB728B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3854450" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11161,21 +11311,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="ZoneTexte 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4434DFEE-8D09-D449-A204-BD55A924562A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3854450" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92BA2357-355F-A847-B99E-D48788DB728B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3854450" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11227,22 +11377,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="ZoneTexte 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74ED3430-1FF5-D046-B0BA-A1298989DB6F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5721350" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BECB4D1-EBF5-4543-9F9A-2DDB882044B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5721350" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11292,21 +11442,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="ZoneTexte 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74ED3430-1FF5-D046-B0BA-A1298989DB6F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5721350" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BECB4D1-EBF5-4543-9F9A-2DDB882044B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5721350" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11358,22 +11508,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="ZoneTexte 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{286B98E5-BF37-8C48-84F7-DB22D5C428DB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7938770" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB611A0-1155-A64A-B558-D59BBE4FF54E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7938770" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11423,21 +11573,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="ZoneTexte 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{286B98E5-BF37-8C48-84F7-DB22D5C428DB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7938770" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB611A0-1155-A64A-B558-D59BBE4FF54E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7938770" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11489,22 +11639,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="ZoneTexte 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1E844B-63D8-7A4B-BFBD-183E464E3847}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10440670" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0554AFC0-D439-7A40-89D5-8E3813742834}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10440670" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11554,21 +11704,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="ZoneTexte 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1E844B-63D8-7A4B-BFBD-183E464E3847}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10440670" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0554AFC0-D439-7A40-89D5-8E3813742834}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10440670" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11620,22 +11770,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="ZoneTexte 8">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E1A1524-56F4-5342-94DD-460BF5F4CE45}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13026390" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C48D286B-C6E6-B747-A5EE-87EFA649753B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13026390" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11685,21 +11835,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="ZoneTexte 8">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E1A1524-56F4-5342-94DD-460BF5F4CE45}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13026390" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C48D286B-C6E6-B747-A5EE-87EFA649753B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13026390" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11751,22 +11901,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="ZoneTexte 9">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16984F06-64BA-2D4B-8514-332ED08369FC}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25652730" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92913276-7F21-C840-99D2-54750B521DF7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25652730" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11816,21 +11966,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="ZoneTexte 9">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16984F06-64BA-2D4B-8514-332ED08369FC}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25652730" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92913276-7F21-C840-99D2-54750B521DF7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25652730" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11882,22 +12032,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="ZoneTexte 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE6FEF86-3F15-2641-B432-4D38513B6E3B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29897070" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E96AF6B-F546-1543-AF04-B90DBB4F0CE5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29897070" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -11947,21 +12097,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="ZoneTexte 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE6FEF86-3F15-2641-B432-4D38513B6E3B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29897070" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E96AF6B-F546-1543-AF04-B90DBB4F0CE5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29897070" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12013,22 +12163,22 @@
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="ZoneTexte 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2ED5ACA-D27B-B144-AA3B-D043DCE53A84}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="807720" y="5709920"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA0C0F04-39DA-1C49-87DE-80C4FC9A4EEB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="807720" y="6535420"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12078,21 +12228,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="ZoneTexte 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2ED5ACA-D27B-B144-AA3B-D043DCE53A84}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="807720" y="5709920"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA0C0F04-39DA-1C49-87DE-80C4FC9A4EEB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="807720" y="6535420"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12144,22 +12294,22 @@
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="ZoneTexte 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59A3DB9B-4C5F-D24E-BE9D-2CA43D9C8692}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3850640" y="5732780"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89704287-484E-3543-B6DC-DE7F22F21F5D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3850640" y="6558280"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12209,21 +12359,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="ZoneTexte 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59A3DB9B-4C5F-D24E-BE9D-2CA43D9C8692}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3850640" y="5732780"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89704287-484E-3543-B6DC-DE7F22F21F5D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3850640" y="6558280"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12275,22 +12425,22 @@
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="ZoneTexte 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34E3559D-E614-6F44-959F-387FD3A32DD1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5725160" y="5717540"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7139E79-75C6-E648-ABD7-3C132FAFE7B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5725160" y="6543040"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12340,21 +12490,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="ZoneTexte 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34E3559D-E614-6F44-959F-387FD3A32DD1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5725160" y="5717540"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7139E79-75C6-E648-ABD7-3C132FAFE7B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5725160" y="6543040"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12406,22 +12556,22 @@
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="ZoneTexte 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C7C186-151F-A44E-A3D6-6617C9016025}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7942580" y="5709920"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99EB8D60-4CEA-D242-9A7C-732654B247EC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7942580" y="6535420"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12471,21 +12621,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="ZoneTexte 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C7C186-151F-A44E-A3D6-6617C9016025}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7942580" y="5709920"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99EB8D60-4CEA-D242-9A7C-732654B247EC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7942580" y="6535420"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12537,22 +12687,22 @@
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="ZoneTexte 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38366437-7667-AF47-84F7-BD2C37E5B4E0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10436860" y="5717540"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{584D3F77-7BF3-634E-A4F7-902A859D7D89}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10436860" y="6543040"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12602,21 +12752,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="ZoneTexte 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38366437-7667-AF47-84F7-BD2C37E5B4E0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10436860" y="5717540"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{584D3F77-7BF3-634E-A4F7-902A859D7D89}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10436860" y="6543040"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12668,22 +12818,22 @@
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="ZoneTexte 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1446D2D4-E27C-0749-B7F0-51D90646D470}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13014960" y="5709920"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E04118B-6A44-A443-BF44-6866EE33AA44}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13014960" y="6535420"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12733,21 +12883,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="ZoneTexte 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1446D2D4-E27C-0749-B7F0-51D90646D470}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13014960" y="5709920"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E04118B-6A44-A443-BF44-6866EE33AA44}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13014960" y="6535420"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12799,22 +12949,22 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="ZoneTexte 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70407851-3306-C445-94A0-C9DBA0DBEF5A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15600680" y="5725160"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2F1E364-E47E-6247-B340-C566248F9E62}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15600680" y="6550660"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12864,21 +13014,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="ZoneTexte 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70407851-3306-C445-94A0-C9DBA0DBEF5A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15600680" y="5725160"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2F1E364-E47E-6247-B340-C566248F9E62}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15600680" y="6550660"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12930,22 +13080,22 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="ZoneTexte 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E42C189D-B0C9-E247-8888-A9B152AD13D9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="21816060" y="5725160"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF5E56F-7981-4843-BFD2-AEF7EA1A7645}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21816060" y="6550660"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12995,21 +13145,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="ZoneTexte 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E42C189D-B0C9-E247-8888-A9B152AD13D9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="21816060" y="5725160"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF5E56F-7981-4843-BFD2-AEF7EA1A7645}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="21816060" y="6550660"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13061,22 +13211,22 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="20" name="ZoneTexte 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5002B184-6C45-E743-A8F4-D613A67B9494}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25656540" y="5725160"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91B778C3-FEF6-1A43-8954-648876841033}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25656540" y="6550660"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13126,21 +13276,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="20" name="ZoneTexte 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5002B184-6C45-E743-A8F4-D613A67B9494}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="25656540" y="5725160"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91B778C3-FEF6-1A43-8954-648876841033}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25656540" y="6550660"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13192,22 +13342,22 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="ZoneTexte 20">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A4939D2-AD03-F04F-9C8F-84A036AF3F81}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29885640" y="5725160"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1D530DC-EDFA-EA43-8EA7-5787DEE042EB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29885640" y="6550660"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13257,21 +13407,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="ZoneTexte 20">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A4939D2-AD03-F04F-9C8F-84A036AF3F81}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29885640" y="5725160"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1D530DC-EDFA-EA43-8EA7-5787DEE042EB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29885640" y="6550660"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13323,22 +13473,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="ZoneTexte 21">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9D825B-533D-C44A-B645-28229152AB3F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="811530" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{901C8334-E527-2D49-A247-C07C67E4A125}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="811530" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13388,21 +13538,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="ZoneTexte 21">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9D825B-533D-C44A-B645-28229152AB3F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="811530" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{901C8334-E527-2D49-A247-C07C67E4A125}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="811530" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13454,22 +13604,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="ZoneTexte 22">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32CCE455-0CC5-A848-A58C-02998F3E4A9D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7938770" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7CCA624-6449-D247-B2D9-E505724B8685}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7938770" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13519,21 +13669,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="ZoneTexte 22">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32CCE455-0CC5-A848-A58C-02998F3E4A9D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7938770" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7CCA624-6449-D247-B2D9-E505724B8685}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7938770" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13585,22 +13735,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="ZoneTexte 23">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC29AA4F-57ED-684A-80AC-096B07559CB4}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10440670" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F6BCC8-2215-E649-B5B7-78A679C6760C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10440670" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13650,21 +13800,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="ZoneTexte 23">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC29AA4F-57ED-684A-80AC-096B07559CB4}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10440670" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F6BCC8-2215-E649-B5B7-78A679C6760C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10440670" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13716,22 +13866,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="ZoneTexte 24">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFAC8F2-E1A0-6649-93D9-03055B1E87AE}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13026390" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FA9E705-540C-4F42-A208-1E36A062FF00}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13026390" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13781,21 +13931,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="ZoneTexte 24">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFAC8F2-E1A0-6649-93D9-03055B1E87AE}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13026390" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FA9E705-540C-4F42-A208-1E36A062FF00}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13026390" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13847,22 +13997,22 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="ZoneTexte 25">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A02D5546-BF61-3248-8FF7-2E87F6D3DE0B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29897070" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{842A4576-CA79-F54C-BA87-F94B251D5A06}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29897070" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13912,21 +14062,21 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="ZoneTexte 25">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A02D5546-BF61-3248-8FF7-2E87F6D3DE0B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="29897070" y="5702300"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{842A4576-CA79-F54C-BA87-F94B251D5A06}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="29897070" y="6527800"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -13974,47 +14124,67 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{05264C8E-9B78-4949-BA0C-C0BF7D87472C}" name="Tableau1" displayName="Tableau1" ref="A6:K16" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A6:K16" xr:uid="{05264C8E-9B78-4949-BA0C-C0BF7D87472C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{05264C8E-9B78-4949-BA0C-C0BF7D87472C}" name="Tableau1" displayName="Tableau1" ref="A2:K12" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:K12" xr:uid="{05264C8E-9B78-4949-BA0C-C0BF7D87472C}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E3BFB1C0-9718-D641-AB6C-3BB13E51615B}" name="Nom de la route"/>
-    <tableColumn id="11" xr3:uid="{F6C7F662-E94D-9246-A526-985014CB4FC6}" name="Controller"/>
-    <tableColumn id="2" xr3:uid="{39B415C7-72F1-B84D-BB31-BAA110BAFA4E}" name="Méthode HTTP"/>
-    <tableColumn id="3" xr3:uid="{F4ADC696-F97D-454C-BA2D-51ABEAD1C696}" name="Chemin"/>
-    <tableColumn id="4" xr3:uid="{6CE70D47-EBF7-004E-934E-8369898687BB}" name="Paramètre de chemin"/>
-    <tableColumn id="5" xr3:uid="{247AF77D-3643-5749-AB9A-D16A5399A338}" name="Paramètres de query"/>
-    <tableColumn id="6" xr3:uid="{BAE1159F-8513-6248-822C-C08B45E0334F}" name="Corps de la requête"/>
-    <tableColumn id="12" xr3:uid="{53A9D4F6-CC29-3F43-B58B-028FB77A039E}" name="Qui a accès"/>
-    <tableColumn id="8" xr3:uid="{FBA98F57-A500-EC47-B89A-73768C27B1F4}" name="Données renvoyées en cas de succès (code 200)"/>
-    <tableColumn id="9" xr3:uid="{2219E770-3452-E842-B6B3-BDCAF8EF3C53}" name="Codes d'erreurs potentiels"/>
-    <tableColumn id="10" xr3:uid="{C84916B4-AEE4-B34B-8FA4-46D79856F062}" name="Description"/>
+    <tableColumn id="1" xr3:uid="{E3BFB1C0-9718-D641-AB6C-3BB13E51615B}" name="Nom de la route" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{F6C7F662-E94D-9246-A526-985014CB4FC6}" name="Controller" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{39B415C7-72F1-B84D-BB31-BAA110BAFA4E}" name="Méthode HTTP" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{F4ADC696-F97D-454C-BA2D-51ABEAD1C696}" name="Chemin" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{6CE70D47-EBF7-004E-934E-8369898687BB}" name="Paramètre de chemin" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{247AF77D-3643-5749-AB9A-D16A5399A338}" name="Paramètres de query" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{BAE1159F-8513-6248-822C-C08B45E0334F}" name="Corps de la requête" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{53A9D4F6-CC29-3F43-B58B-028FB77A039E}" name="Qui a accès" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{FBA98F57-A500-EC47-B89A-73768C27B1F4}" name="Données renvoyées en cas de succès (code 200)" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{2219E770-3452-E842-B6B3-BDCAF8EF3C53}" name="Codes d'erreurs potentiels" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{C84916B4-AEE4-B34B-8FA4-46D79856F062}" name="Description" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97642F72-841B-7A45-93EE-D7100A7D0B5A}" name="Tableau13" displayName="Tableau13" ref="A7:K17" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A7:K17" xr:uid="{97642F72-841B-7A45-93EE-D7100A7D0B5A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97642F72-841B-7A45-93EE-D7100A7D0B5A}" name="Tableau13" displayName="Tableau13" ref="A2:K12" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A2:K12" xr:uid="{97642F72-841B-7A45-93EE-D7100A7D0B5A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{597C7967-3D89-EC41-9F43-DFDD96094024}" name="Nom de la route"/>
-    <tableColumn id="11" xr3:uid="{DB2EBFA4-8858-384B-A460-A589C19BA940}" name="Controller"/>
-    <tableColumn id="2" xr3:uid="{6F4408C8-81F6-2346-A76D-4AEEBF3714AF}" name="Méthode HTTP"/>
-    <tableColumn id="3" xr3:uid="{CBEEF7F2-C96C-EA40-AB5D-A6C3270659D9}" name="Chemin"/>
-    <tableColumn id="4" xr3:uid="{2751F8BA-1A4F-F54A-B91B-FF8F24003745}" name="Paramètre de chemin"/>
-    <tableColumn id="5" xr3:uid="{70FB293F-1A64-9E4F-975C-61CB4F157992}" name="Paramètres de query"/>
-    <tableColumn id="6" xr3:uid="{F705E039-62DF-1B4E-B1A8-064233C625B9}" name="Corps de la requête"/>
-    <tableColumn id="12" xr3:uid="{93AB885C-FE86-F04D-BBD8-9480558907BD}" name="Qui a accès"/>
-    <tableColumn id="8" xr3:uid="{E1D45A26-2938-C847-8043-0D30F30B4A9E}" name="Données renvoyées en cas de succès (code 200)"/>
-    <tableColumn id="9" xr3:uid="{D3220630-B964-1A42-8876-C52428C69856}" name="Codes d'erreurs potentiels"/>
-    <tableColumn id="10" xr3:uid="{2F8E7B3A-132A-3247-BEE2-65DF4363007C}" name="Description"/>
+    <tableColumn id="1" xr3:uid="{597C7967-3D89-EC41-9F43-DFDD96094024}" name="Nom de la route" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{DB2EBFA4-8858-384B-A460-A589C19BA940}" name="Controller" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{6F4408C8-81F6-2346-A76D-4AEEBF3714AF}" name="Méthode HTTP" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{CBEEF7F2-C96C-EA40-AB5D-A6C3270659D9}" name="Chemin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{2751F8BA-1A4F-F54A-B91B-FF8F24003745}" name="Paramètre de chemin" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{70FB293F-1A64-9E4F-975C-61CB4F157992}" name="Paramètres de query" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F705E039-62DF-1B4E-B1A8-064233C625B9}" name="Corps de la requête" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{93AB885C-FE86-F04D-BBD8-9480558907BD}" name="Qui a accès" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{E1D45A26-2938-C847-8043-0D30F30B4A9E}" name="Données renvoyées en cas de succès (code 200)" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{D3220630-B964-1A42-8876-C52428C69856}" name="Codes d'erreurs potentiels" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{2F8E7B3A-132A-3247-BEE2-65DF4363007C}" name="Description" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D2E791C4-8DA3-D44F-A4B6-F415523A6AF3}" name="Tableau134" displayName="Tableau134" ref="A7:K18" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B6F9A8EE-2DD6-8441-AAB3-A18D62EC0FAE}" name="Tableau1345" displayName="Tableau1345" ref="A7:K18" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A7:K18" xr:uid="{B6F9A8EE-2DD6-8441-AAB3-A18D62EC0FAE}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{42E5814F-4302-0440-B652-DC2DAE0322CD}" name="Nom de la route"/>
+    <tableColumn id="11" xr3:uid="{AF7ED20C-A3C2-5A48-93DE-D1EF571CE957}" name="Controller"/>
+    <tableColumn id="2" xr3:uid="{547F3C25-30EF-264B-B01A-D15D51945BFB}" name="Méthode HTTP"/>
+    <tableColumn id="3" xr3:uid="{4B2BC952-5167-1B4C-8E53-3C1C9068B533}" name="Chemin"/>
+    <tableColumn id="4" xr3:uid="{F850DFC5-7942-5E4F-9FC9-03A3F981B837}" name="Paramètre de chemin"/>
+    <tableColumn id="5" xr3:uid="{D253FCFF-728C-2845-A6E4-31F721F726C9}" name="Paramètres de query"/>
+    <tableColumn id="6" xr3:uid="{4F4E3777-D3E4-7A42-8AC4-8F1DE76DC04B}" name="Corps de la requête"/>
+    <tableColumn id="12" xr3:uid="{9171FB7B-0B32-C242-8B3F-604BF8B9778C}" name="Qui a accès"/>
+    <tableColumn id="8" xr3:uid="{391D6285-A180-BC4E-8F96-562A84DF71FA}" name="Données renvoyées en cas de succès (code 200)"/>
+    <tableColumn id="9" xr3:uid="{1AE869C4-0CB4-0D40-8E0A-B71D6AD32856}" name="Codes d'erreurs potentiels"/>
+    <tableColumn id="10" xr3:uid="{596F36FE-788B-8D4E-AFD9-021BF7BE33E9}" name="Description"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D2E791C4-8DA3-D44F-A4B6-F415523A6AF3}" name="Tableau134" displayName="Tableau134" ref="A7:K18" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A7:K18" xr:uid="{D2E791C4-8DA3-D44F-A4B6-F415523A6AF3}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{B025A220-00F1-024D-B04B-61220E233D67}" name="Nom de la route"/>
@@ -14028,26 +14198,6 @@
     <tableColumn id="8" xr3:uid="{77CD987E-1BBE-894F-9A01-A6BD74D47E0F}" name="Données renvoyées en cas de succès (code 200)"/>
     <tableColumn id="9" xr3:uid="{0963B99F-FB15-E841-89C6-7703B6CE3371}" name="Codes d'erreurs potentiels"/>
     <tableColumn id="10" xr3:uid="{373F0664-2DF1-DE49-A4DA-74872D24A8F8}" name="Description"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B6F9A8EE-2DD6-8441-AAB3-A18D62EC0FAE}" name="Tableau1345" displayName="Tableau1345" ref="A7:K18" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A7:K18" xr:uid="{B6F9A8EE-2DD6-8441-AAB3-A18D62EC0FAE}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{42E5814F-4302-0440-B652-DC2DAE0322CD}" name="Nom de la route"/>
-    <tableColumn id="11" xr3:uid="{AF7ED20C-A3C2-5A48-93DE-D1EF571CE957}" name="Controller"/>
-    <tableColumn id="2" xr3:uid="{547F3C25-30EF-264B-B01A-D15D51945BFB}" name="Méthode HTTP"/>
-    <tableColumn id="3" xr3:uid="{4B2BC952-5167-1B4C-8E53-3C1C9068B533}" name="Chemin"/>
-    <tableColumn id="4" xr3:uid="{F850DFC5-7942-5E4F-9FC9-03A3F981B837}" name="Paramètre de chemin"/>
-    <tableColumn id="5" xr3:uid="{D253FCFF-728C-2845-A6E4-31F721F726C9}" name="Paramètres de query"/>
-    <tableColumn id="6" xr3:uid="{4F4E3777-D3E4-7A42-8AC4-8F1DE76DC04B}" name="Corps de la requête"/>
-    <tableColumn id="12" xr3:uid="{9171FB7B-0B32-C242-8B3F-604BF8B9778C}" name="Qui a accès"/>
-    <tableColumn id="8" xr3:uid="{391D6285-A180-BC4E-8F96-562A84DF71FA}" name="Données renvoyées en cas de succès (code 200)"/>
-    <tableColumn id="9" xr3:uid="{1AE869C4-0CB4-0D40-8E0A-B71D6AD32856}" name="Codes d'erreurs potentiels"/>
-    <tableColumn id="10" xr3:uid="{596F36FE-788B-8D4E-AFD9-021BF7BE33E9}" name="Description"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14370,438 +14520,404 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A719E83-66A7-E24C-B37B-5836C81120CA}">
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="1" max="1" width="38.77734375" customWidth="1"/>
     <col min="2" max="3" width="25" customWidth="1"/>
     <col min="4" max="6" width="33.33203125" customWidth="1"/>
-    <col min="7" max="7" width="35.5" customWidth="1"/>
-    <col min="8" max="8" width="40.1640625" customWidth="1"/>
-    <col min="9" max="10" width="50" customWidth="1"/>
+    <col min="7" max="7" width="34.77734375" customWidth="1"/>
+    <col min="8" max="8" width="40.109375" customWidth="1"/>
+    <col min="9" max="9" width="63" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
     <col min="11" max="11" width="64" customWidth="1"/>
     <col min="12" max="12" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="10"/>
     </row>
-    <row r="2" spans="1:11" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="15"/>
+    <row r="2" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18" t="s">
+    <row r="3" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18" t="s">
+    <row r="8" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6" t="s">
+    <row r="9" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
+      <c r="F11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J12" t="s">
-        <v>56</v>
-      </c>
-      <c r="K12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" t="s">
-        <v>69</v>
-      </c>
-      <c r="K14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K15" t="s">
-        <v>62</v>
-      </c>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:K1"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14814,108 +14930,456 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5344883-53BA-C340-9D1C-63CB3A93C05F}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:L12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="1" max="1" width="38.77734375" customWidth="1"/>
     <col min="2" max="3" width="25" customWidth="1"/>
     <col min="4" max="6" width="33.33203125" customWidth="1"/>
-    <col min="7" max="7" width="35.5" customWidth="1"/>
-    <col min="8" max="8" width="40.1640625" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" customWidth="1"/>
+    <col min="8" max="8" width="40.109375" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
     <col min="11" max="11" width="64" customWidth="1"/>
     <col min="12" max="12" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="66.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C251D17-FD4C-AE4D-A5DF-C0C8F234FD87}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38.77734375" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="6" width="33.33203125" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" customWidth="1"/>
+    <col min="8" max="8" width="40.109375" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="12" max="12" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:11" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:11" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="15"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
     </row>
-    <row r="3" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="22"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
     </row>
-    <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
-    </row>
-    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
@@ -14933,10 +15397,10 @@
         <v>8</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>9</v>
@@ -14945,258 +15409,54 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K8" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H9" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" t="s">
-        <v>105</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="80" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" t="s">
-        <v>94</v>
-      </c>
-      <c r="I11" t="s">
-        <v>95</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>89</v>
-      </c>
-      <c r="F13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" t="s">
-        <v>90</v>
-      </c>
-      <c r="J13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F16" t="s">
         <v>4</v>
       </c>
       <c r="G16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15220,110 +15480,110 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D962928-8205-D244-A24F-E770CB9538C3}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="1" max="1" width="38.77734375" customWidth="1"/>
     <col min="2" max="3" width="25" customWidth="1"/>
     <col min="4" max="6" width="33.33203125" customWidth="1"/>
-    <col min="7" max="7" width="35.5" customWidth="1"/>
-    <col min="8" max="8" width="40.1640625" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" customWidth="1"/>
+    <col min="8" max="8" width="40.109375" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
     <col min="11" max="11" width="64" customWidth="1"/>
     <col min="12" max="12" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:11" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:11" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="15"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
     </row>
-    <row r="3" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="22"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
     </row>
-    <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
-    </row>
-    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
@@ -15341,10 +15601,10 @@
         <v>8</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>9</v>
@@ -15353,18 +15613,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
@@ -15376,30 +15636,30 @@
         <v>4</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>4</v>
@@ -15408,33 +15668,33 @@
         <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="H9" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="I9" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="K9" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>4</v>
@@ -15443,33 +15703,33 @@
         <v>4</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="K10" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>4</v>
@@ -15478,36 +15738,36 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="H11" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="K11" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="K12" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F16" t="s">
         <v>4</v>
       </c>
@@ -15515,7 +15775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
         <v>4</v>
       </c>
@@ -15536,210 +15796,6 @@
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C251D17-FD4C-AE4D-A5DF-C0C8F234FD87}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="38.83203125" customWidth="1"/>
-    <col min="2" max="3" width="25" customWidth="1"/>
-    <col min="4" max="6" width="33.33203125" customWidth="1"/>
-    <col min="7" max="7" width="35.5" customWidth="1"/>
-    <col min="8" max="8" width="40.1640625" customWidth="1"/>
-    <col min="9" max="10" width="50" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
-    <col min="12" max="12" width="50" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="10"/>
-    </row>
-    <row r="2" spans="1:11" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="15"/>
-    </row>
-    <row r="3" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
-    </row>
-    <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
-    </row>
-    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>146</v>
-      </c>
-      <c r="E8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" t="s">
-        <v>147</v>
-      </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" t="s">
-        <v>148</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:K4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">

--- a/table_des_routes-exemple-2.xlsx
+++ b/table_des_routes-exemple-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\begin\OneDrive\Documents\VINCI_bloc1\HTML\Projet_TypeScript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC4819F-54D2-4B71-90AA-0D7ED4336E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42EE370-8DEC-431B-8F04-D66A2A09E54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="1" xr2:uid="{6911F376-5DDD-4D7B-A61B-D86E41227354}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6911F376-5DDD-4D7B-A61B-D86E41227354}"/>
   </bookViews>
   <sheets>
     <sheet name="Module 1   Users" sheetId="2" r:id="rId1"/>
@@ -476,9 +476,6 @@
     <t xml:space="preserve">400: id doit être un nombre                                                                      404: User inéxistant avec ce id                                                              400: User est un Admin, impossible de l'inactiver                                                          403 : accès interdit  </t>
   </si>
   <si>
-    <t xml:space="preserve">400 : User invalide                                                                                 403 : accès interdit                                                                              404: User introuvable                                                                           400: id doit être un nombre </t>
-  </si>
-  <si>
     <t>400 : username déjà existant                                                            400: email déjà éxistant                                                                      400:  User Invalide</t>
   </si>
   <si>
@@ -586,6 +583,9 @@
 403 : accès refusé
 404 : jeu introuvable</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">400 : User invalide                                                                                 403 : accès interdit                                                                                  404: User introuvable                                                                           400: id doit être un nombre </t>
   </si>
 </sst>
 </file>
@@ -14124,40 +14124,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{05264C8E-9B78-4949-BA0C-C0BF7D87472C}" name="Tableau1" displayName="Tableau1" ref="A2:K12" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{05264C8E-9B78-4949-BA0C-C0BF7D87472C}" name="Tableau1" displayName="Tableau1" ref="A2:K12" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A2:K12" xr:uid="{05264C8E-9B78-4949-BA0C-C0BF7D87472C}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E3BFB1C0-9718-D641-AB6C-3BB13E51615B}" name="Nom de la route" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{F6C7F662-E94D-9246-A526-985014CB4FC6}" name="Controller" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{39B415C7-72F1-B84D-BB31-BAA110BAFA4E}" name="Méthode HTTP" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{F4ADC696-F97D-454C-BA2D-51ABEAD1C696}" name="Chemin" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{6CE70D47-EBF7-004E-934E-8369898687BB}" name="Paramètre de chemin" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{247AF77D-3643-5749-AB9A-D16A5399A338}" name="Paramètres de query" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{BAE1159F-8513-6248-822C-C08B45E0334F}" name="Corps de la requête" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{53A9D4F6-CC29-3F43-B58B-028FB77A039E}" name="Qui a accès" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{FBA98F57-A500-EC47-B89A-73768C27B1F4}" name="Données renvoyées en cas de succès (code 200)" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{2219E770-3452-E842-B6B3-BDCAF8EF3C53}" name="Codes d'erreurs potentiels" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{C84916B4-AEE4-B34B-8FA4-46D79856F062}" name="Description" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{E3BFB1C0-9718-D641-AB6C-3BB13E51615B}" name="Nom de la route" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{F6C7F662-E94D-9246-A526-985014CB4FC6}" name="Controller" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{39B415C7-72F1-B84D-BB31-BAA110BAFA4E}" name="Méthode HTTP" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{F4ADC696-F97D-454C-BA2D-51ABEAD1C696}" name="Chemin" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6CE70D47-EBF7-004E-934E-8369898687BB}" name="Paramètre de chemin" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{247AF77D-3643-5749-AB9A-D16A5399A338}" name="Paramètres de query" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{BAE1159F-8513-6248-822C-C08B45E0334F}" name="Corps de la requête" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{53A9D4F6-CC29-3F43-B58B-028FB77A039E}" name="Qui a accès" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{FBA98F57-A500-EC47-B89A-73768C27B1F4}" name="Données renvoyées en cas de succès (code 200)" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{2219E770-3452-E842-B6B3-BDCAF8EF3C53}" name="Codes d'erreurs potentiels" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{C84916B4-AEE4-B34B-8FA4-46D79856F062}" name="Description" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97642F72-841B-7A45-93EE-D7100A7D0B5A}" name="Tableau13" displayName="Tableau13" ref="A2:K12" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97642F72-841B-7A45-93EE-D7100A7D0B5A}" name="Tableau13" displayName="Tableau13" ref="A2:K12" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:K12" xr:uid="{97642F72-841B-7A45-93EE-D7100A7D0B5A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{597C7967-3D89-EC41-9F43-DFDD96094024}" name="Nom de la route" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{DB2EBFA4-8858-384B-A460-A589C19BA940}" name="Controller" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{6F4408C8-81F6-2346-A76D-4AEEBF3714AF}" name="Méthode HTTP" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{CBEEF7F2-C96C-EA40-AB5D-A6C3270659D9}" name="Chemin" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{2751F8BA-1A4F-F54A-B91B-FF8F24003745}" name="Paramètre de chemin" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{70FB293F-1A64-9E4F-975C-61CB4F157992}" name="Paramètres de query" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F705E039-62DF-1B4E-B1A8-064233C625B9}" name="Corps de la requête" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{93AB885C-FE86-F04D-BBD8-9480558907BD}" name="Qui a accès" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{E1D45A26-2938-C847-8043-0D30F30B4A9E}" name="Données renvoyées en cas de succès (code 200)" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{D3220630-B964-1A42-8876-C52428C69856}" name="Codes d'erreurs potentiels" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{2F8E7B3A-132A-3247-BEE2-65DF4363007C}" name="Description" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{597C7967-3D89-EC41-9F43-DFDD96094024}" name="Nom de la route" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{DB2EBFA4-8858-384B-A460-A589C19BA940}" name="Controller" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{6F4408C8-81F6-2346-A76D-4AEEBF3714AF}" name="Méthode HTTP" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{CBEEF7F2-C96C-EA40-AB5D-A6C3270659D9}" name="Chemin" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{2751F8BA-1A4F-F54A-B91B-FF8F24003745}" name="Paramètre de chemin" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{70FB293F-1A64-9E4F-975C-61CB4F157992}" name="Paramètres de query" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{F705E039-62DF-1B4E-B1A8-064233C625B9}" name="Corps de la requête" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{93AB885C-FE86-F04D-BBD8-9480558907BD}" name="Qui a accès" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{E1D45A26-2938-C847-8043-0D30F30B4A9E}" name="Données renvoyées en cas de succès (code 200)" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{D3220630-B964-1A42-8876-C52428C69856}" name="Codes d'erreurs potentiels" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{2F8E7B3A-132A-3247-BEE2-65DF4363007C}" name="Description" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14615,7 +14615,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>27</v>
@@ -14685,7 +14685,7 @@
         <v>46</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>120</v>
@@ -14720,7 +14720,7 @@
         <v>46</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>121</v>
@@ -14790,7 +14790,7 @@
         <v>59</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>41</v>
@@ -14807,10 +14807,10 @@
         <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>4</v>
@@ -14822,18 +14822,18 @@
         <v>25</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -14842,10 +14842,10 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>4</v>
@@ -14857,10 +14857,10 @@
         <v>123</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>127</v>
@@ -14980,7 +14980,7 @@
     </row>
     <row r="3" spans="1:12" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>49</v>
@@ -14992,7 +14992,7 @@
         <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>4</v>
@@ -15001,13 +15001,13 @@
         <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>52</v>
@@ -15015,7 +15015,7 @@
     </row>
     <row r="4" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>49</v>
@@ -15024,10 +15024,10 @@
         <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>4</v>
@@ -15042,7 +15042,7 @@
         <v>73</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>74</v>
@@ -15051,7 +15051,7 @@
     </row>
     <row r="5" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>49</v>
@@ -15187,7 +15187,7 @@
     </row>
     <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>49</v>
@@ -15805,14 +15805,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b627c0e-478a-4aac-b169-4af5291f66a0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82ddd626-5708-4755-b8ca-246d358bf7f1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16043,27 +16041,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b627c0e-478a-4aac-b169-4af5291f66a0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82ddd626-5708-4755-b8ca-246d358bf7f1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A209F81-EE97-47D1-BB68-CF14A79E1188}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A45C50-903C-42B9-99B5-3FAEB4FE670B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="82ddd626-5708-4755-b8ca-246d358bf7f1"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8b627c0e-478a-4aac-b169-4af5291f66a0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16088,9 +16079,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A45C50-903C-42B9-99B5-3FAEB4FE670B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A209F81-EE97-47D1-BB68-CF14A79E1188}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="82ddd626-5708-4755-b8ca-246d358bf7f1"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8b627c0e-478a-4aac-b169-4af5291f66a0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>